--- a/data/trans_orig/IP07A04-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A04-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse por su aspecto en 2007 (tasa de respuesta: 99,3%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el adulto en 2007 (tasa de respuesta: 99,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20602</t>
+          <t>19494</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12213</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14252</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>29090</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26377</t>
+          <t>26046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42099</t>
+          <t>42686</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13801</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28500</t>
+          <t>27141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44318</t>
+          <t>43378</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65271</t>
+          <t>64967</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31707</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48322</t>
+          <t>48642</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31852</t>
+          <t>32400</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49312</t>
+          <t>49534</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68466</t>
+          <t>68693</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>92601</t>
+          <t>92666</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9802</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22008</t>
+          <t>22090</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24075</t>
+          <t>24125</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39758</t>
+          <t>39777</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37260</t>
+          <t>37407</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57298</t>
+          <t>57328</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>18107</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33025</t>
+          <t>32740</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32288</t>
+          <t>32433</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50526</t>
+          <t>49822</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56249</t>
+          <t>55296</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>78835</t>
+          <t>77589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40146</t>
+          <t>39953</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58929</t>
+          <t>59512</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23764</t>
+          <t>23674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39526</t>
+          <t>40237</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68905</t>
+          <t>68947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94857</t>
+          <t>95323</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36882</t>
+          <t>35447</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55266</t>
+          <t>55758</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33311</t>
+          <t>33266</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51169</t>
+          <t>51815</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75555</t>
+          <t>75074</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100875</t>
+          <t>102460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45837</t>
+          <t>45241</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67058</t>
+          <t>66173</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45531</t>
+          <t>44432</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65696</t>
+          <t>63998</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>94656</t>
+          <t>95433</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124670</t>
+          <t>123625</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26176</t>
+          <t>26956</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26861</t>
+          <t>26458</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43119</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43576</t>
+          <t>43703</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64779</t>
+          <t>65005</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31275</t>
+          <t>32974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32680</t>
+          <t>33249</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51399</t>
+          <t>50655</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54835</t>
+          <t>54064</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78555</t>
+          <t>78431</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50572</t>
+          <t>51842</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74204</t>
+          <t>74318</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30407</t>
+          <t>30021</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48628</t>
+          <t>49038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86384</t>
+          <t>86815</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116815</t>
+          <t>116827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>66468</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93486</t>
+          <t>92096</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50730</t>
+          <t>50747</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72556</t>
+          <t>74141</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123997</t>
+          <t>126304</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>158374</t>
+          <t>159235</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82020</t>
+          <t>81727</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>107992</t>
+          <t>107388</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81438</t>
+          <t>81067</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>107225</t>
+          <t>107778</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>172884</t>
+          <t>170972</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>210288</t>
+          <t>208064</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26367</t>
+          <t>26799</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45152</t>
+          <t>44060</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54210</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78504</t>
+          <t>77970</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86481</t>
+          <t>86857</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115890</t>
+          <t>116769</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39119</t>
+          <t>39419</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59507</t>
+          <t>61079</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70983</t>
+          <t>70448</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>96422</t>
+          <t>95761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116142</t>
+          <t>116446</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148654</t>
+          <t>148827</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse por su aspecto en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>17688</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33322</t>
+          <t>32323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>8797</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19685</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29474</t>
+          <t>28463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47760</t>
+          <t>48148</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25215</t>
+          <t>25568</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42788</t>
+          <t>42283</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>21254</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37522</t>
+          <t>36706</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51598</t>
+          <t>51604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74362</t>
+          <t>74647</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29983</t>
+          <t>30122</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47705</t>
+          <t>47632</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29969</t>
+          <t>30278</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47106</t>
+          <t>46860</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>64901</t>
+          <t>64556</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>90313</t>
+          <t>89178</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>14797</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29251</t>
+          <t>28892</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34153</t>
+          <t>34616</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37836</t>
+          <t>37301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59694</t>
+          <t>58375</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29058</t>
+          <t>29224</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47246</t>
+          <t>47265</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40473</t>
+          <t>39343</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59409</t>
+          <t>58343</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74975</t>
+          <t>74018</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101294</t>
+          <t>101163</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44530</t>
+          <t>45690</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64760</t>
+          <t>65537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34870</t>
+          <t>33721</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53892</t>
+          <t>53224</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85633</t>
+          <t>84721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113490</t>
+          <t>113509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23624</t>
+          <t>24069</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40178</t>
+          <t>40980</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21929</t>
+          <t>21639</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38042</t>
+          <t>38061</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50522</t>
+          <t>50137</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73457</t>
+          <t>73046</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36822</t>
+          <t>37012</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56209</t>
+          <t>55909</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33335</t>
+          <t>33644</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>74266</t>
+          <t>75151</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>101396</t>
+          <t>101585</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23108</t>
+          <t>22539</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>15932</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30283</t>
+          <t>29213</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29913</t>
+          <t>29778</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49264</t>
+          <t>48978</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25039</t>
+          <t>25343</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30503</t>
+          <t>30341</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48627</t>
+          <t>48086</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44975</t>
+          <t>46428</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68212</t>
+          <t>67885</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66826</t>
+          <t>66054</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92452</t>
+          <t>91765</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46533</t>
+          <t>45506</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68682</t>
+          <t>68107</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120395</t>
+          <t>119886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155142</t>
+          <t>152392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54437</t>
+          <t>54333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77657</t>
+          <t>79489</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47865</t>
+          <t>47777</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69842</t>
+          <t>70884</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105746</t>
+          <t>106867</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139984</t>
+          <t>139708</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72429</t>
+          <t>71869</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>97839</t>
+          <t>97399</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67149</t>
+          <t>68539</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>94246</t>
+          <t>94108</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>146845</t>
+          <t>147013</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>183305</t>
+          <t>182933</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28639</t>
+          <t>28432</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48846</t>
+          <t>47411</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38943</t>
+          <t>38706</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>59590</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70402</t>
+          <t>72512</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99130</t>
+          <t>99753</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45299</t>
+          <t>45333</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67988</t>
+          <t>67829</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75103</t>
+          <t>74891</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101677</t>
+          <t>102079</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127323</t>
+          <t>124729</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>161553</t>
+          <t>160392</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse por su aspecto en 2016 (tasa de respuesta: 98,82%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el adulto en 2016 (tasa de respuesta: 98,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>24454</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41332</t>
+          <t>41620</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28301</t>
+          <t>27528</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45080</t>
+          <t>46061</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56644</t>
+          <t>55513</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81671</t>
+          <t>80275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28248</t>
+          <t>28353</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46023</t>
+          <t>46262</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21329</t>
+          <t>20641</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37345</t>
+          <t>36621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54010</t>
+          <t>54262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77998</t>
+          <t>77894</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27004</t>
+          <t>26647</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44023</t>
+          <t>44589</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21384</t>
+          <t>21227</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37153</t>
+          <t>37119</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>51864</t>
+          <t>52372</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76146</t>
+          <t>74282</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25008</t>
+          <t>25024</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41517</t>
+          <t>41507</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27266</t>
+          <t>26650</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44525</t>
+          <t>45482</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56841</t>
+          <t>56759</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81125</t>
+          <t>82450</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40213</t>
+          <t>40089</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59508</t>
+          <t>59834</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48680</t>
+          <t>48486</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69121</t>
+          <t>69627</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95684</t>
+          <t>94467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123442</t>
+          <t>123460</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42314</t>
+          <t>42475</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62012</t>
+          <t>62637</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22559</t>
+          <t>21518</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38423</t>
+          <t>38783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69978</t>
+          <t>70016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98583</t>
+          <t>95851</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29182</t>
+          <t>28984</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47604</t>
+          <t>47416</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27462</t>
+          <t>27689</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45164</t>
+          <t>45225</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60222</t>
+          <t>61020</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85021</t>
+          <t>86124</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31347</t>
+          <t>31832</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49754</t>
+          <t>49786</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27221</t>
+          <t>28124</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45748</t>
+          <t>46306</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63428</t>
+          <t>64207</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88538</t>
+          <t>90345</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10212</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23095</t>
+          <t>23464</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28409</t>
+          <t>27776</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46512</t>
+          <t>46148</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41973</t>
+          <t>42058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64435</t>
+          <t>65810</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16948</t>
+          <t>16627</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32285</t>
+          <t>31711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27253</t>
+          <t>27089</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45434</t>
+          <t>45532</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48704</t>
+          <t>48201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72358</t>
+          <t>72093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71226</t>
+          <t>70523</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98116</t>
+          <t>97732</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54322</t>
+          <t>53435</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79978</t>
+          <t>79024</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>134098</t>
+          <t>133352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>170419</t>
+          <t>168585</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61167</t>
+          <t>61310</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86473</t>
+          <t>86487</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52083</t>
+          <t>52224</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76713</t>
+          <t>75911</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119994</t>
+          <t>120892</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>155770</t>
+          <t>155668</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63180</t>
+          <t>63387</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>87819</t>
+          <t>88962</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52978</t>
+          <t>51784</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76352</t>
+          <t>77913</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120948</t>
+          <t>122928</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>157065</t>
+          <t>157261</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37960</t>
+          <t>39071</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58947</t>
+          <t>61045</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59820</t>
+          <t>60032</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85935</t>
+          <t>85814</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>105440</t>
+          <t>104300</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>138798</t>
+          <t>139384</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62067</t>
+          <t>60844</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>86540</t>
+          <t>85661</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>81576</t>
+          <t>82233</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>109938</t>
+          <t>109746</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>150267</t>
+          <t>150346</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>188656</t>
+          <t>189458</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A04-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A04-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el adulto en 2007 (tasa de respuesta: 99,3%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7130</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12497</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>13414</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8438</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19494</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8788</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19973</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>10,52%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7130</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3700</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12221</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13951</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29090</t>
+          <t>28392</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20008</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14533</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28185</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,27%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,37%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20,11%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>33466</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26046</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>42686</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>25771</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>41793</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>26,24%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>33,47%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20008</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14174</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>27141</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>14,27%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43378</t>
+          <t>43893</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64967</t>
+          <t>64610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>40319</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>31569</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49773</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>28,76%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>22,52%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>35,5%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>39909</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>31392</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>48642</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>31757</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>48912</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>31,29%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>24,61%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>38,14%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>40319</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>32400</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>49534</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>28,76%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68693</t>
+          <t>68563</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>92666</t>
+          <t>92395</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,51%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>31799</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23809</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>40417</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>22,68%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,98%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>15332</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10327</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22090</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10296</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21968</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>12,02%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,32%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>31799</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>24125</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>39777</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>22,68%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37407</t>
+          <t>38032</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57328</t>
+          <t>58205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -1174,72 +1174,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40932</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33277</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>50534</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>29,2%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>23,74%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>36,05%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>25427</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18107</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>32740</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>18904</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>33801</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>19,94%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>25,67%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>40932</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>32433</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>49822</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>29,2%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55296</t>
+          <t>56315</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77589</t>
+          <t>78875</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140189</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>140189</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>140189</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>140189</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>140189</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>140189</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31021</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23717</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39830</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>49450</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>39953</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>59512</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>39455</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>59626</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>25,58%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,67%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>31021</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>23674</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>40237</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68947</t>
+          <t>67279</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95323</t>
+          <t>93744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>41671</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>33158</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>51719</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>20,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>16,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>25,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>46119</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>35447</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>55758</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>37328</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>56144</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>23,86%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>28,84%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>41671</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>33266</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>51815</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>20,51%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75074</t>
+          <t>74363</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102460</t>
+          <t>100672</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>54308</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>44509</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>64540</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>26,73%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>21,9%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>31,76%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>55167</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>45241</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>66173</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>45923</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>64785</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>28,54%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>23,4%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>34,23%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>54308</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>44432</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>63998</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>26,73%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>95433</t>
+          <t>96224</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>123625</t>
+          <t>123950</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,26%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34342</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26170</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>44385</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,9%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>19050</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13162</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>26956</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>13977</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>26878</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,86%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,94%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>34342</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>26458</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>43271</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,9%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43703</t>
+          <t>43650</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65005</t>
+          <t>64802</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>41864</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33005</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>51802</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>16,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>25,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>23519</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>17439</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>32974</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>17386</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>31812</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>12,17%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>41864</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>33249</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>50655</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>20,6%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54064</t>
+          <t>54308</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78431</t>
+          <t>78862</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>203206</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>203206</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>203206</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>193304</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>193304</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>193304</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>203206</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>203206</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>203206</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38152</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>29604</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>49186</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14,32%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>62864</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>51842</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>74318</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>52002</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>74789</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>19,59%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>16,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>38152</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>30021</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>49038</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86815</t>
+          <t>85810</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116827</t>
+          <t>115900</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>61679</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>52014</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>74548</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>17,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>15,15%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>21,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>79584</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>66468</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>92096</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>67245</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>93212</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>24,8%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20,72%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>28,7%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>61679</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>50747</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>74141</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126304</t>
+          <t>124658</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>159235</t>
+          <t>158813</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -2317,67 +2317,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>94627</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>82007</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>108145</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>27,56%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>23,88%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>31,49%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>95076</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>81727</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>107388</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>81202</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>108377</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>29,63%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>25,47%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>33,47%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>94627</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>81067</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>107778</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>27,56%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>170972</t>
+          <t>170869</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>208064</t>
+          <t>208560</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>66141</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>55590</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>78771</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>19,26%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>16,19%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>22,94%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>34382</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>26799</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>44060</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>26318</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>44115</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>10,72%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>13,73%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>66141</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>54210</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>77970</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>19,26%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86857</t>
+          <t>86324</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116769</t>
+          <t>114549</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>82796</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>71532</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>95089</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>24,11%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>20,83%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>27,69%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>48946</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>39419</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>61079</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>39223</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>61300</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>15,25%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>12,29%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>19,04%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>82796</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>70448</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>95761</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>24,11%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116446</t>
+          <t>116655</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148827</t>
+          <t>151493</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>343395</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>343395</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>343395</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>476</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>320852</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>320852</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>320852</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>343395</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>343395</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>343395</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13559</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8742</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19942</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>24438</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17688</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>32323</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17105</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>32800</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>15,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13559</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8797</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>20992</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,69%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28463</t>
+          <t>29638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48148</t>
+          <t>48163</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28659</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21344</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>37508</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,68%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>33423</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>25568</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>42283</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24571</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>42467</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>21,49%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,44%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>27,19%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28659</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>21254</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>36706</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>18,37%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51604</t>
+          <t>51677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74647</t>
+          <t>75424</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>38328</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29726</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>47823</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>24,56%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>19,05%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>30,65%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>38339</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>30122</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>47632</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>29603</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>48215</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>24,65%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>19,37%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>30,63%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>38328</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>30278</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>46860</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>24,56%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>64556</t>
+          <t>65409</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89178</t>
+          <t>90618</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26085</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18576</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>34142</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16,72%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,9%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,88%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>21244</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14797</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>28892</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14634</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>29104</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>13,66%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26085</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18342</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>34616</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>16,72%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37301</t>
+          <t>37367</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58375</t>
+          <t>58911</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49418</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>41254</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>60601</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31,67%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>26,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>38,83%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>38070</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>29224</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>47265</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>30475</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>47595</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>24,48%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>30,39%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>49418</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>39343</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>58343</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>31,67%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74018</t>
+          <t>74233</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101163</t>
+          <t>101654</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156049</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156049</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156049</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>156049</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>156049</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>156049</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>43150</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34508</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>52565</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24,63%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>30,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>55083</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>45690</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>65537</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>45244</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>65392</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>33,08%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>39,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>43150</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>33721</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>53224</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>24,63%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84721</t>
+          <t>83512</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113509</t>
+          <t>112896</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29343</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>21986</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>38085</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>16,75%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>21,73%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>31819</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24069</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>40980</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>24139</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>40350</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>19,11%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>14,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>24,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>29343</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>21639</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>38061</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>16,75%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50137</t>
+          <t>50600</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73046</t>
+          <t>72352</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>41982</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32984</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>50912</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>23,96%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>18,82%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>29,06%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>46207</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37012</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55909</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>37042</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>55788</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>27,75%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>22,23%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>33,57%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>41982</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>33644</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>52510</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>23,96%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>75151</t>
+          <t>76695</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>101585</t>
+          <t>101736</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22099</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15806</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30043</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,15%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>15960</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10637</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22539</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10886</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23280</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,58%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>22099</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15932</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>29213</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29778</t>
+          <t>29150</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48978</t>
+          <t>49111</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38652</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>29951</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>48648</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>22,06%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17,09%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>27,76%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>17451</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11540</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25343</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>11995</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>25212</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>10,48%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,22%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38652</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>30341</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>48086</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>22,06%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46428</t>
+          <t>45776</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67885</t>
+          <t>67787</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>175227</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>175227</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>175227</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166521</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166521</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166521</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>175227</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>175227</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>175227</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>56710</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>46946</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>68420</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>17,12%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,17%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20,65%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>79522</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>66054</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>91765</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>66597</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>93130</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>24,69%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>20,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>28,5%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>56710</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>45506</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>68107</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>17,12%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119886</t>
+          <t>119977</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152392</t>
+          <t>155279</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -4475,107 +4475,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>58003</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>69012</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>17,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14,26%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20,83%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>65242</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>54333</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>79489</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>54183</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>77632</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>20,26%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>16,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>24,68%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>58003</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>47777</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>70884</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>17,51%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>24,11%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>123245</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>108082</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>139838</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>18,86%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>21,4%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>123245</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>106867</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>139708</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>18,86%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>16,36%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>80310</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>67846</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>93247</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>24,24%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>20,48%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>28,15%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>84546</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>71869</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>97399</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>72241</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>98422</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>26,25%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>22,32%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>30,24%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>80310</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>68539</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>94108</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>24,24%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>147013</t>
+          <t>145320</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>182933</t>
+          <t>181949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>48185</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>37886</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>59858</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>11,44%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>18,07%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>37204</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>28432</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>47411</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>28552</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>47564</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>11,55%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>14,72%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>48185</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>38706</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>59590</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>14,55%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72512</t>
+          <t>72401</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99753</t>
+          <t>101198</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>88069</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>75937</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>101606</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>26,58%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>22,92%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>30,67%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>55521</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>45333</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>67829</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>44466</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>68202</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>17,24%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>14,08%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>21,06%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>88069</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>74891</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>102079</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>26,58%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124729</t>
+          <t>127010</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>160392</t>
+          <t>163385</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>331277</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>331277</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>331277</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>457</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>322036</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>322036</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>322036</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>331277</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>331277</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>331277</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el adulto en 2016 (tasa de respuesta: 98,82%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36330</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27934</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>45595</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19,4%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,34%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>31874</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24454</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>41620</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23285</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>40150</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>17,14%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>22,38%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>36330</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>27528</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>46061</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>19,4%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55513</t>
+          <t>56245</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80275</t>
+          <t>81481</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28019</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20733</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>37438</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>19,99%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>36653</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28353</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>46262</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>29018</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>46393</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>19,71%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,24%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>24,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28019</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>20641</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>36621</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>14,96%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54262</t>
+          <t>53469</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77894</t>
+          <t>77534</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28599</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21135</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37045</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>15,27%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11,28%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19,78%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>34921</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>26647</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>44589</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>44544</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>18,78%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>14,33%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>23,97%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28599</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21227</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>37119</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52372</t>
+          <t>51044</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>74282</t>
+          <t>75870</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>35686</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26704</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>44801</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,05%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,26%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>32618</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25024</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>41507</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>24780</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>41493</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>17,54%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,32%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>35686</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>26650</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>45482</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,05%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56759</t>
+          <t>56267</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82450</t>
+          <t>80687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -5726,72 +5726,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>58679</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48069</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>69786</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31,33%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>25,66%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>37,26%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>49917</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>40089</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>59834</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>40306</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>59911</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>26,84%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>32,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>58679</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>48486</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>69627</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>31,33%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94467</t>
+          <t>95022</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123460</t>
+          <t>124658</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29981</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22006</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39624</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,64%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>52519</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>42475</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>62637</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>43857</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>62820</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>30,97%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>29981</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>21518</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>38783</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70016</t>
+          <t>69083</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95851</t>
+          <t>95570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35495</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26658</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>45422</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>20,39%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>15,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>26,1%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>37311</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>28984</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>47416</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>28931</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>46975</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>22,01%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>27,97%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>35495</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>27689</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>45225</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>20,39%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61020</t>
+          <t>61160</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86124</t>
+          <t>85982</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35889</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27534</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>45407</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>20,62%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>15,82%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>26,09%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>40228</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>31832</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>49786</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>31765</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>50010</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>23,73%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>29,36%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35889</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>28124</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>46306</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>20,62%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64207</t>
+          <t>63619</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>90345</t>
+          <t>89913</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36436</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27320</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>45721</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20,93%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,7%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>15743</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10229</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23464</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9965</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23195</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,28%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>36436</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>27776</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>46148</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>20,93%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42058</t>
+          <t>40720</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65810</t>
+          <t>64360</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -6408,72 +6408,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>36248</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27728</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>46455</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>20,83%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>26,69%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>23754</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16627</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31711</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>16665</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>32046</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>14,01%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,81%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>18,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>36248</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>27089</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>45532</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>20,83%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48201</t>
+          <t>48671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72093</t>
+          <t>72424</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>169553</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>169553</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>169553</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>66311</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>53968</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>79433</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,35%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>84393</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>70523</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>97732</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>71465</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>97030</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>23,74%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>27,49%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>66311</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>53435</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>79024</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>18,35%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133352</t>
+          <t>131997</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>168585</t>
+          <t>168414</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>63514</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>51935</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>76056</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>17,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14,37%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>21,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>73964</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>61310</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>86487</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>62059</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>87824</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>20,8%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>24,33%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>63514</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>52224</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>75911</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>17,58%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>120892</t>
+          <t>120491</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>155668</t>
+          <t>156880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>64488</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>53679</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>78486</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>17,85%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>14,85%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>21,72%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>75148</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>63387</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>88962</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>63683</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>88008</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>21,14%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>17,83%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>25,02%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>64488</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>51784</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>77913</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>17,85%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>122928</t>
+          <t>122504</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>157261</t>
+          <t>158430</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>72122</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>59407</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>86342</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>19,96%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>16,44%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>23,89%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>48361</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>39071</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>61045</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>38125</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>59735</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>13,6%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>10,99%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>17,17%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>72122</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>60032</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>85814</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>19,96%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>104300</t>
+          <t>104256</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>139384</t>
+          <t>138188</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>94927</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>81685</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>108751</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>26,27%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>22,6%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>30,09%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>73670</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>60844</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>85661</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>61492</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>86789</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>20,72%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>17,11%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>24,09%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>94927</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>82233</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>109746</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>26,27%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>150346</t>
+          <t>148392</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>189458</t>
+          <t>187707</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>508</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>355536</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>355536</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>355536</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
